--- a/www/download/COUNTRY.CHE.zdW16.xlsx
+++ b/www/download/COUNTRY.CHE.zdW16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Suíça</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>1.68667687110171</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>1.68576706430227</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>1.55340960876531</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>1.34547860388246</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>1.24197099209246</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1.24295856500799</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>1.25298030886987</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>1.19910848713805</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>1.07766842423887</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>1.08300343364318</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>1.04029358370705</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>0.88508870449828</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.937233392187754</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>0.926577700560784</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.915088705743353</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>4.012</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4.118</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>4.146</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>4.134</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>4.165</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>4.205</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>4.286</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>4.398</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>4.502</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>4.58</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>4.683</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>4.89</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>4.96</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>5.022</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>5.085</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>3.332</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3.425</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>3.451</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>3.431</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>3.448</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>3.466</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>3.541</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>3.647</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>3.724</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>3.742</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>3.828</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>4.002</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>4.06</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>4.109</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>4.161</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>7403.791</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>7335.74</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>7274.751</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>7307.236</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>7454.801</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>7494.642</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>7589.781</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>7717.644</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>7866.345</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>7857.804</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>7890.129</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>8045.498</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>8089.34</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>8100.645</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>8210.192</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6057.222</t>
+          <t>9198092515.02885</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6007.552</t>
+          <t>8885204829.14715</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>5970.524</t>
+          <t>8748009043.62626</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5982.301</t>
+          <t>8997282499.94534</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>6094.74</t>
+          <t>8842401184.84076</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6098.211</t>
+          <t>9113180700.07789</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>6189.574</t>
+          <t>9527247206.71712</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>6325.867</t>
+          <t>9452911178.99477</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>6443.864</t>
+          <t>9787338471.08483</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>6348.042</t>
+          <t>9179906503.67377</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>6370.689</t>
+          <t>8926595112.38423</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>6497.347</t>
+          <t>10260755509.9174</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>6534.815</t>
+          <t>10164183397.4483</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>6536.929</t>
+          <t>10402918318.5927</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>6628.596</t>
+          <t>10372484654.484</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>4116811699.80754</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4019557832.30607</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>4057082749.99276</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>4325747819.60452</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>4169426797.69074</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>4122148834.75073</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>4146011461.41684</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>4016016454.99168</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>4176749800.78725</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>3910871090.73012</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>3964539912.68512</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>4364882069.26363</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>4289221154.2796</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>4559933628.10334</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>4582790218.46574</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1298616.99204875</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1242517.54541876</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1111497.92614114</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>985097.60654953</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>846231.612390098</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>847474.751927398</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>839347.432036565</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>737052.245509597</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>641931.155150088</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>631186.181551595</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>573113.362928485</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>552351.758117642</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>577736.243996628</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>566841.652720204</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>541210.66219947</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>32725.2007380877</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>31655.8119619704</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>31323.9849720191</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>34098.8589189727</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>38176.3165273641</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>41646.2681981743</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>44811.7864870946</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>50904.8162319131</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>56220.2585407691</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>50881.3925964188</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>56823.368504341</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>62158.896492103</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>61332.7283842943</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>61093.293847904</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>62128.6643176508</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>83439.0226165601</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>79420.4982949458</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>78769.3468311652</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>88199.8351867378</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>95524.8262550325</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>106334.280499828</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>117470.097158161</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>130746.047902688</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>147644.664782059</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>126557.533323748</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>135965.813485056</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>166636.924366824</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>161241.458165547</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>164071.781130501</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>164162.895145874</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.471338123209078</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.494580312221404</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.471629830574853</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.382951861615207</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.461769278063739</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.479376714540383</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.492898429635505</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.575159631663686</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.54279387259094</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.623178533050264</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.60691760968683</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.488550411419507</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.523543497746634</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.433557927183905</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.446410523722199</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.68667687110171</t>
+          <t>1235.5332753326</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.68576706430227</t>
+          <t>1173.63464772666</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.55340960876531</t>
+          <t>1175.55610318859</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.34547860388246</t>
+          <t>1260.71688424613</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.24197099209246</t>
+          <t>1209.13267101958</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1.24295856500799</t>
+          <t>1189.39452562147</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1.25298030886987</t>
+          <t>1170.98029121257</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1.19910848713805</t>
+          <t>1101.25754403344</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1.07766842423887</t>
+          <t>1121.60783287049</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.08300343364318</t>
+          <t>1045.06628566232</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.04029358370705</t>
+          <t>1035.78616611317</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.88508870449828</t>
+          <t>1090.77439059016</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.937233392187754</t>
+          <t>1056.51982585185</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.926577700560784</t>
+          <t>1109.80179238113</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.915088705743353</t>
+          <t>1101.44401244541</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>6305878264.22051</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>6168870431.3747</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>7099559810.2255</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>7703083304.60401</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>8049401107.94482</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>8080994349.73711</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>8633508473.31996</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>9161912581.60623</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>9479301394.31956</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>9305998788.53048</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>9380423714.50723</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>10581729959.2303</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>10405575307.1205</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>10531616275.5638</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.389</t>
+          <t>10963788552.4026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>3314760243.74669</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>3202657988.7765</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>3954352832.40033</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>4301396141.26975</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>4661059671.77811</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>4448937197.93257</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>4854087104.92711</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>4949569906.67533</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.332</t>
+          <t>5398109705.56018</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>5137200127.13258</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.361</t>
+          <t>5584332531.49532</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>6327352762.05686</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.419</t>
+          <t>6272219605.22535</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>6453872458.7521</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.443</t>
+          <t>6898515413.43089</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.777</t>
+          <t>2991118020.47382</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>2966212442.5982</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.826</t>
+          <t>3145206977.82517</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.974</t>
+          <t>3401687163.33426</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>3388341436.16671</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1.089</t>
+          <t>3632057151.80454</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1.119</t>
+          <t>3779421368.39285</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1.237</t>
+          <t>4212342674.9309</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>4081191688.75937</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.506</t>
+          <t>4168798661.3979</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>3796091183.0119</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1.923</t>
+          <t>4254377197.17348</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1.878</t>
+          <t>4133355701.89514</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>4077743816.81172</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2.013</t>
+          <t>4065273138.97167</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.526</t>
+          <t>1817.88721049024</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.539</t>
+          <t>1754.09123823316</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>1729.98342896665</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>1743.51076203791</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.773</t>
+          <t>1767.47299159958</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.807</t>
+          <t>1759.56256560621</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.852</t>
+          <t>1748.15463788537</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.954</t>
+          <t>1734.65642742658</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.114</t>
+          <t>1730.40969200259</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.083</t>
+          <t>1696.32916050166</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.154</t>
+          <t>1664.42303019726</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1.382</t>
+          <t>1623.67266787884</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1.328</t>
+          <t>1609.65391091699</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1.364</t>
+          <t>1590.96515707088</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>1.399</t>
+          <t>1593.14021089184</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>1845.29466077244</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>1781.32742496932</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>1754.55100367033</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>1767.49282499865</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.379</t>
+          <t>1789.67148273949</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>1782.40991081352</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>1770.96891493904</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.459</t>
+          <t>1754.72825838303</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.533</t>
+          <t>1747.42549342914</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>1715.63873440415</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.561</t>
+          <t>1684.73343819514</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.674</t>
+          <t>1645.1678383347</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.643</t>
+          <t>1630.77029579081</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.663</t>
+          <t>1613.1694103994</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.681</t>
+          <t>1614.69492678474</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>118192.946258789</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>118749.870683384</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>125928.512856047</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>144897.872215318</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>171592.362829954</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>186224.949965637</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>208905.780762122</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>248224.945741381</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>285888.285651839</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>257326.237092498</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>286276.174133076</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>339251.025052533</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>329991.170874116</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>334971.042858862</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>352569.594747377</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2163459142.65496</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2083534044.7046</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2029436807.54278</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2050834269.76752</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2136949295.2289</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2182956335.06757</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2472412774.36124</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2546863590.71103</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2675491546.95639</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2317349360.50663</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>2377249953.76025</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>2806341479.51912</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>2753670778.80811</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2751792356.20569</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2939928767.4043</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>101231.140926005</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>103422.296633826</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>103828.646839031</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>119035.927269302</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>139929.132497766</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>151813.601725536</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>165973.434875797</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>189710.011870013</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>215019.49246889</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>191319.871479162</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>212137.01197349</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>254524.64524331</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>246451.141992427</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>256763.794455706</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>265507.044778291</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>7403.791</t>
+          <t>6149727588.30897</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>7335.74</t>
+          <t>6070817453.19406</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>7274.751</t>
+          <t>5963665129.42729</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>7307.236</t>
+          <t>6262302418.17446</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>7454.801</t>
+          <t>6291018284.88101</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>7494.642</t>
+          <t>6424361068.78658</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>7589.781</t>
+          <t>6758427016.01125</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>7717.644</t>
+          <t>6627840304.08327</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>7866.345</t>
+          <t>6782314727.13766</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>7857.804</t>
+          <t>6002793182.38777</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>7890.129</t>
+          <t>6129954931.47777</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>8045.498</t>
+          <t>7299568157.75068</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>8089.34</t>
+          <t>7116002867.96135</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>8100.645</t>
+          <t>7569527959.04502</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>8210.192</t>
+          <t>7603952228.52874</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6057.222</t>
+          <t>16961.8053327845</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>6007.552</t>
+          <t>15327.5740495586</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>5970.524</t>
+          <t>22099.8660170158</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>5982.301</t>
+          <t>25861.9449460154</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>6094.74</t>
+          <t>31663.2303321885</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>6098.211</t>
+          <t>34411.3482401014</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>6189.574</t>
+          <t>42932.3458863247</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>6325.867</t>
+          <t>58514.9338713685</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>6443.864</t>
+          <t>70868.7931829489</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>6348.042</t>
+          <t>66006.3656133358</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>6370.689</t>
+          <t>74139.1621595864</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>6497.347</t>
+          <t>84726.3798092229</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>6534.815</t>
+          <t>83540.0288816891</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>6536.929</t>
+          <t>78207.2484031561</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>6628.596</t>
+          <t>87062.5499690858</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>11056.571</t>
+          <t>-3986268445.65401</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10672.277</t>
+          <t>-3987283408.48945</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>10526.886</t>
+          <t>-3934228321.88451</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>10777.033</t>
+          <t>-4211468148.40695</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>10517.03</t>
+          <t>-4154068989.6521</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>10913.449</t>
+          <t>-4241404733.71901</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>11370.433</t>
+          <t>-4286014241.65001</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>11201.406</t>
+          <t>-4080976713.37224</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>11643.453</t>
+          <t>-4106823180.18127</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>11121.539</t>
+          <t>-3685443821.88114</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>10785.911</t>
+          <t>-3752704977.71752</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>12444.015</t>
+          <t>-4493226678.23155</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>12373.467</t>
+          <t>-4362332089.15324</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>12531.619</t>
+          <t>-4817735602.83933</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>10372.485</t>
+          <t>-4664023461.12444</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>106945.370176976</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>112686.584100604</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>124477.307109724</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>144238.532839738</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>160439.706776468</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>165226.62691434</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>172397.005097031</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>189538.487424096</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>223213.328117734</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>216127.426873831</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>232183.413331073</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>282349.005430389</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>269056.381050813</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>277743.269359678</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>284418.462861643</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3607.538</t>
+          <t>0.108748339404249</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3541.509</t>
+          <t>0.113806207554397</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>3478.796</t>
+          <t>0.118985660750935</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>3478.431</t>
+          <t>0.116142361406405</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>3533.849</t>
+          <t>0.128126426774103</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>3569.216</t>
+          <t>0.132391696212089</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>3634.397</t>
+          <t>0.140750786272264</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>3680.407</t>
+          <t>0.146163574977071</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>3726.831</t>
+          <t>0.138137523314672</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>3690.704</t>
+          <t>0.124726587299337</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>3730.638</t>
+          <t>0.125779013053219</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>3827.466</t>
+          <t>0.12156164057238</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>3866.233</t>
+          <t>0.119269254466818</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>3873.601</t>
+          <t>0.119224793470026</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>3925.544</t>
+          <t>0.118012751422974</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>159013.807839256</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>161506.796123523</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>174343.978557172</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>204274.930223031</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>218870.414806918</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>222748.280044263</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>228679.229974057</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>249970.071984687</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>296972.509600384</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>295420.895290237</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>317641.843833139</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>387459.450856882</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>368851.830352167</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>378146.058253246</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>389253.428599351</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4786.923</t>
+          <t>175068.339479657</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>4654.408</t>
+          <t>177542.289264167</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>4707.963</t>
+          <t>192018.658221289</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>5006.151</t>
+          <t>225708.653287684</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>4808.478</t>
+          <t>242664.270561385</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>4788.055</t>
+          <t>248315.58159179</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>4810.139</t>
+          <t>255019.836659806</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>4632.177</t>
+          <t>278431.373819329</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>4837.716</t>
+          <t>331616.056997717</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>4595.27</t>
+          <t>334724.071850213</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>4652.214</t>
+          <t>360523.762265751</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>5150.7</t>
+          <t>439751.54938027</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>5075.758</t>
+          <t>419022.034017657</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>5332.645</t>
+          <t>429750.632077853</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>4582.79</t>
+          <t>442941.399661282</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>26.54</t>
+          <t>776679.759012353</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>29.07</t>
+          <t>786154.772669633</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>825880.569415599</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>973594.036236475</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>1060391.57377992</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>1088755.89216615</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>28.68</t>
+          <t>1119107.53864174</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>36.56</t>
+          <t>1237333.47775683</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>1460683.642851</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>38.14</t>
+          <t>1506433.79002768</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>36.94</t>
+          <t>1595339.2815254</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>26.14</t>
+          <t>1923231.17137278</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>1877856.13407336</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>22.58</t>
+          <t>1952322.87670861</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>44.64</t>
+          <t>2013272.65260047</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.578</t>
+          <t>196091.573870958</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.501</t>
+          <t>196858.813990454</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.351</t>
+          <t>196220.581594008</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.191</t>
+          <t>197113.00732618</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.019</t>
+          <t>195010.477432922</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.024</t>
+          <t>197742.997259173</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.011</t>
+          <t>200618.686362081</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.883</t>
+          <t>204703.506562058</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>214663.934268545</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.781</t>
+          <t>215572.930942041</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.707</t>
+          <t>222360.746165464</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>229421.629022315</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.713</t>
+          <t>231102.165916226</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>233766.11726052</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>0.541</t>
+          <t>238322.865685925</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>178163.090093593</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>179120.457210816</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>178219.191393294</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>178477.348659599</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>175914.566833184</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>177407.938496236</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>179953.991603912</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>183864.613866482</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>192312.674733246</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>190121.029853443</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>195912.405479859</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>202348.952806483</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>203588.668207571</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>205941.550243278</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>209698.841849703</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>84462.6340414859</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>89469.2932283201</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>98267.9452532732</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>113075.510419697</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>135864.183329789</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>144142.239324783</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>157515.265987042</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>180853.084547751</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>201775.22076969</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>187892.345622558</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>200660.200315297</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>233791.136392015</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>223970.501106871</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>232765.29176239</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>237591.845098011</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>6057222000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>6007552000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>5970524000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>5982301000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>6094740000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>6098211000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>6189574000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>6325867000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>6443864000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>6348042000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>6370689000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>6497347000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>6534815000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>6536929000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>6628596000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>7403790883.86285</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>7335739689.91635</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>7274750953.336</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>7307236001.83675</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>7454801395.14908</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>7494641544.79047</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>7589781265.81113</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>7717644071.29197</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>7866345152.98363</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>7857803829.99937</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>7890128958.4337</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>8045497538.40311</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>8089339836.82285</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>8100644729.34871</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>8210192468.06948</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>3607537750.59297</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3541508544.43799</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>3478796192.19108</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>3478431291.51233</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>3533848945.12316</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>3569215551.08921</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>3634396990.94106</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>3680407279.16667</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>3726830902.30611</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>3690704255.56561</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>3730637801.94872</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>3827466463.96165</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>3866233328.92341</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>3873600574.90945</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>3925543690.4045</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4012254</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4118131</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4146218</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4134238</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>4165458</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4204780</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>4285666</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>4398199</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>4501677</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>4580104</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>4683310</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>4890381</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>4960441</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>5021571</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>5084671</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>3332012</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3424880</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>3451203</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>3431181</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>3448279</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>3465754</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>3540633</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>3646755</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>3723895</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>3742223</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>3827566</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>4001636</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>4059764</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>4108782</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>4160711</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>7403790883.86285</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>7335739689.91635</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>7274750953.336</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>7307236001.83675</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>7454801395.14908</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>7494641544.79047</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>7589781265.81113</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>7717644071.29197</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>7866345152.98363</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>7857803829.99937</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>7890128958.4337</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>8045497538.40311</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>8089339836.82285</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>8100644729.34871</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>8210192468.06948</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>6057222000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>6007552000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>5970524000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>5982301000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>6094740000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>6098211000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>6189574000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>6325867000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>6443864000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>6348042000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>6370689000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>6497347000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>6534815000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>6536929000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>6628596000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>526268.540498316</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>539312.73068399</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>590382.851847539</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>685264.780212253</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>773286.464113235</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>806794.705256368</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>852014.304657695</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>954347.867043238</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1113686.14605307</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1082598.6718767</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1153707.31813328</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1381729.93724796</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1327569.4702692</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>1363645.05879035</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>1398665.13522947</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>259530.985971618</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>267011.605034143</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>290286.575793508</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>338784.159991228</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>378528.455501533</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>392457.802412324</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>412535.137763118</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>459284.451695462</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>533391.248073703</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>522616.412855948</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>561184.001993006</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>673542.680123105</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>642992.495646632</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>662515.924919476</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>680533.250223279</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>871990.297299345</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>870667.536626781</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>837399.672577266</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>845903.009631242</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>846178.466644104</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>861995.59706102</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>879728.74098412</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>910738.524059442</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>947937.900961193</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>972777.165992631</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>983959.645078411</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>1002218.54133092</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1031932.82661148</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>1057295.24125307</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>1074832.90936098</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
